--- a/01-03-01/one-line-card-example.xlsx
+++ b/01-03-01/one-line-card-example.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시1 정육점·식당 대표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시1 반찬가게 대표" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시2 강사 본인" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시3 직장인" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시4 프리랜서" sheetId="4" state="visible" r:id="rId4"/>
@@ -482,14 +482,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>예시 ① 정육점 · 식당 대표님 (사람에게 맡기다 멈추기 직전)</t>
+          <t>예시 ① 반찬가게 대표님 (사람에게 맡기다 멈추기 직전, 지어낸 예시)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>「맡긴 일」「그때 일」은 첫 통화에서 대표님이 한 말이에요. 나머지는 그 말을 가·나·다에 대어 본 판정이에요.</t>
+          <t>지어낸 예시예요.</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>직원에게 레시피와 고기 자르는 법 맡기기 (아주 접지는 않았지만 대표님이 손을 못 떼는 상태)</t>
+          <t>직원에게 반찬 간 맞추는 법과 포장하는 법 맡기기 (아주 접지는 않았지만 대표님이 손을 못 떼는 상태)</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
           <t>나는 어디서 멈췄나 (첫 번째 가 · 두 번째 나 · 세 번째 다)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>나 결과를 뭉뚱그려 말하고 탓하며 접기</t>
         </is>
@@ -547,9 +547,9 @@
           <t>다음엔 이것부터</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>문제가 나면 직원 탓 대신 돌아보고, 대표님 머릿속의 고기 자르는 기준을 매뉴얼에 반영해요</t>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>문제가 나면 직원 탓 대신 돌아보고, 대표님 머릿속의 간 맞추는 기준을 매뉴얼에 반영해요</t>
         </is>
       </c>
     </row>
@@ -559,16 +559,16 @@
           <t>한 줄로 옮기기</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>「나는 직원에게 고기 손질을 맡기다 두 번째 공통점에서 멈추는 사람이다. 다음엔 실수를 매뉴얼에 반영하는 것부터.」</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>「나는 직원에게 반찬 만들기를 맡기다 두 번째 공통점에서 멈추는 사람이다. 다음엔 실수를 매뉴얼에 반영하는 것부터.」</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>색칠한 칸은 예시를 완성하려고 채운 값(거버 판정·지어낸 예시)이에요.</t>
+          <t>지어낸 예시예요. 색칠한 칸은 예시를 완성하려고 채운 값이에요.</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>고칠 점마다 피드백을 계속 줌 → 잘 나온 걸 스킬로 만들어 달라고 함(다를 넘김) → 다음 카드뉴스부터 그 퀄리티로 나와요</t>
+          <t>고칠 점마다 피드백을 계속 줬어요 → 잘 나온 걸 스킬로 만들어 달라고 했어요(세 번째 공통점을 넘었어요) → 다음 카드뉴스부터 그 퀄리티로 나와요</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>처음 한 달은 고칠 때마다 「이거 매뉴얼에 반영해 줘」까지 말해요</t>
+          <t>고칠 때마다 「이거 매뉴얼에 반영해 줘」까지 말해요</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>색칠한 칸은 예시를 완성하려고 채운 값(거버 판정·지어낸 예시)이에요.</t>
+          <t>지어낸 예시예요. 색칠한 칸은 예시를 완성하려고 채운 값이에요.</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>색칠한 칸은 예시를 완성하려고 채운 값(거버 판정·지어낸 예시)이에요.</t>
+          <t>지어낸 예시예요. 색칠한 칸은 예시를 완성하려고 채운 값이에요.</t>
         </is>
       </c>
     </row>

--- a/01-03-01/one-line-card-example.xlsx
+++ b/01-03-01/one-line-card-example.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>매뉴얼 없이 직접 보여 주며 「이렇게 이렇게 해라」 했는데, 문제가 생기면 직원을 나무라게 됐어요. 대표님이 없으면 가게가 엉망이 될 것 같다고 하세요</t>
+          <t>매뉴얼 없이 직접 보여 주며 이렇게 이렇게 하라고 가르쳤는데, 문제가 생기면 직원을 나무라게 됐어요. 대표님이 없으면 가게가 엉망이 될 것 같다고 하세요</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>나 (여기서 「좀 바꿔 줘」 하고 접을 수 있었던 자리)</t>
+          <t>나 (여기서 그냥 바꿔 달라고만 하고 접을 수 있었던 자리)</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>처음 두세 번 우리 팀 양식에 맞게 고쳐 주다가 「매번 고칠 거면 내가 쓰는 게 빠르다」 하고 다시 직접 썼어요</t>
+          <t>처음 두세 번 우리 팀 양식에 맞게 고쳐 주다가 매번 고칠 거면 내가 쓰는 게 빠르겠다 싶어 다시 직접 썼어요</t>
         </is>
       </c>
     </row>

--- a/01-03-01/one-line-card-example.xlsx
+++ b/01-03-01/one-line-card-example.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시1 반찬가게 대표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시1 카페 대표" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시2 강사 본인" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시3 직장인" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시4 프리랜서" sheetId="4" state="visible" r:id="rId4"/>
@@ -482,7 +482,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>예시 ① 반찬가게 대표님 (사람에게 맡기다 멈추기 직전, 지어낸 예시)</t>
+          <t>예시 ① 카페 대표님 (알바생에게 맡기다 멈추기 직전, 지어낸 예시)</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>직원에게 반찬 간 맞추는 법과 포장하는 법 맡기기 (아주 접지는 않았지만 대표님이 손을 못 떼는 상태)</t>
+          <t>알바생에게 마감 정리와 재료 주문 맡기기 (아주 접지는 않았지만 대표님이 퇴근 전에 다시 확인하는 상태)</t>
         </is>
       </c>
     </row>
@@ -525,19 +525,19 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>매뉴얼 없이 직접 보여 주며 이렇게 이렇게 하라고 가르쳤는데, 문제가 생기면 직원을 나무라게 됐어요. 대표님이 없으면 가게가 엉망이 될 것 같다고 하세요</t>
+          <t>재료가 모자란 날이 생기자 「왜 이것도 못 챙겨」 하고 말하게 됐어요. 어떻게 챙기라는 건지는 따로 적어 준 적이 없어요</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>나는 어디서 멈췄나 (첫 번째 가 · 두 번째 나 · 세 번째 다)</t>
+          <t>나는 어디서 멈췄나 (첫 번째 · 두 번째 · 세 번째)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>나 결과를 뭉뚱그려 말하고 탓하며 접기</t>
+          <t>두 번째 결과를 뭉뚱그려 말하고 탓하며 접기</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>문제가 나면 직원 탓 대신 돌아보고, 대표님 머릿속의 간 맞추는 기준을 매뉴얼에 반영해요</t>
+          <t>탓하는 말 대신 재료 확인 순서를 적어 주고, 모자랐던 날의 원인을 그 순서에 반영해요</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>「나는 직원에게 반찬 만들기를 맡기다 두 번째 공통점에서 멈추는 사람이다. 다음엔 실수를 매뉴얼에 반영하는 것부터.」</t>
+          <t>「나는 알바생에게 마감 정리를 맡기다 두 번째 공통점에서 멈추는 사람이다. 다음엔 모자랐던 날의 원인을 순서에 반영하는 것부터.」</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>나 (여기서 그냥 바꿔 달라고만 하고 접을 수 있었던 자리)</t>
+          <t>두 번째 (여기서 그냥 바꿔 달라고만 하고 접을 수 있었던 자리)</t>
         </is>
       </c>
     </row>
@@ -744,12 +744,12 @@
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>나는 어디서 멈췄나 (첫 번째 가 · 두 번째 나 · 세 번째 다)</t>
+          <t>나는 어디서 멈췄나 (첫 번째 · 두 번째 · 세 번째)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>가 한 번 세팅이면 끝이라 생각하기</t>
+          <t>첫 번째 한 번 세팅이면 끝이라 생각하기</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>나는 어디서 멈췄나 (첫 번째 가 · 두 번째 나 · 세 번째 다)</t>
+          <t>나는 어디서 멈췄나 (첫 번째 · 두 번째 · 세 번째)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>다 좋은 결과를 스킬로 안 남기기</t>
+          <t>세 번째 좋은 결과를 스킬로 안 남기기</t>
         </is>
       </c>
     </row>
